--- a/Edexcel_A_Level_Maths_RAG.xlsx
+++ b/Edexcel_A_Level_Maths_RAG.xlsx
@@ -104,15 +104,15 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="003B5BDB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="009CA3AF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="003B5BDB"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -515,18 +515,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1012,6 +1012,15 @@
 Source: Question Set 7: Algebraic Methods exam questions</t>
       </text>
     </comment>
+    <comment ref="J10" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (a,b) (page 1)
+Question 3 (page 1)
+Question 7 (a,c) (page 1)
+Question 8 (c) (page 1)
+Source: 2a. Mixed exam-style questions on proof</t>
+      </text>
+    </comment>
     <comment ref="N10" authorId="0" shapeId="0">
       <text>
         <t>Page 1: the question starting there (a)
@@ -1080,6 +1089,19 @@
 Source: Exam Booklet</t>
       </text>
     </comment>
+    <comment ref="J15" authorId="0" shapeId="0">
+      <text>
+        <t>Question 4 (page 1)
+Question 5 (page 1)
+Question 6 (page 1)
+Question 7 (page 1)
+Question 8 (page 2)
+Question 9 (page 2)
+Question 10 (page 2)
+Question 11 (page 2)
+Source: 01a. Indices</t>
+      </text>
+    </comment>
     <comment ref="N15" authorId="0" shapeId="0">
       <text>
         <t>Page 4: the question starting there
@@ -1098,6 +1120,19 @@
 Question 9 (page 3)
 Question 11 (page 4)
 Source: A Level Maths: Algebraic Expressions — Medium</t>
+      </text>
+    </comment>
+    <comment ref="J16" authorId="0" shapeId="0">
+      <text>
+        <t>Question 4 (page 1)
+Question 5 (page 1)
+Question 7 (page 1)
+Question 8 (page 1)
+Question 9 (page 2)
+Question 11 (page 2)
+Question 12 (page 2)
+Question 15 (page 2)
+Source: 02a. Surds</t>
       </text>
     </comment>
     <comment ref="N16" authorId="0" shapeId="0">
@@ -1227,6 +1262,12 @@
 Source: Ch1 Algebraic Expression Exam Questions</t>
       </text>
     </comment>
+    <comment ref="J22" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Source: 08a. Simultaneous equations</t>
+      </text>
+    </comment>
     <comment ref="G23" authorId="0" shapeId="0">
       <text>
         <t>Question 3 (page 2)
@@ -1237,6 +1278,15 @@
 Source: Question Set 3: Equations and Inequalities exam questions</t>
       </text>
     </comment>
+    <comment ref="J23" authorId="0" shapeId="0">
+      <text>
+        <t>Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Source: 08a. Simultaneous equations</t>
+      </text>
+    </comment>
     <comment ref="N23" authorId="0" shapeId="0">
       <text>
         <t>Page 8: the question starting there (b)
@@ -1248,6 +1298,13 @@
         <t>Question 8 (b) (page 6)
 Question 13 (page 8)
 Source: Question Set 3: Equations and Inequalities exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Source: 09a. Inequalities</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
@@ -1305,6 +1362,17 @@
 Source: Exam Booklet</t>
       </text>
     </comment>
+    <comment ref="J27" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 6 (page 1)
+Source: 11a. Polynomials</t>
+      </text>
+    </comment>
     <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>Question 11 (page 6)
@@ -1322,6 +1390,13 @@
       <text>
         <t>Page 5: the question starting there (a)
 Source: Ch4 Graphs and Transformations + Ch7 Algebraic Methods Exam Questions 1</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 4 (page 1)
+Source: 02a. Rational expressions</t>
       </text>
     </comment>
     <comment ref="G30" authorId="0" shapeId="0">
@@ -1391,6 +1466,19 @@
 Source: Question Set 9: Differentiation exam questions</t>
       </text>
     </comment>
+    <comment ref="J32" authorId="0" shapeId="0">
+      <text>
+        <t>Question 2 (page 1)
+Question 3 (page 1)
+Question 5 (page 1)
+Question 6 (page 2)
+Question 8 (page 2)
+Question 9 (page 2)
+Question 10 (page 2)
+Question 13 (page 2)
+Source: 02a. Rational expressions</t>
+      </text>
+    </comment>
     <comment ref="N32" authorId="0" shapeId="0">
       <text>
         <t>Page 15: the question starting there (a)
@@ -1445,6 +1533,12 @@
 Source: Ch4 Graphs and Transformations + Ch7 Algebraic Methods Exam Questions 1</t>
       </text>
     </comment>
+    <comment ref="J35" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (b) (page 1)
+Source: 14a. Graphs of functions</t>
+      </text>
+    </comment>
     <comment ref="G36" authorId="0" shapeId="0">
       <text>
         <t>Question 2 (a) (page 3)
@@ -1661,6 +1755,19 @@
 Source: Question Set 4: Graphs and Transformations exam questions</t>
       </text>
     </comment>
+    <comment ref="J44" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (a,b) (page 1)
+Question 2 (b) (page 1)
+Question 3 (a,c) (page 1)
+Question 4 (a,b) (page 1)
+Question 7 (a) (page 2)
+Question 9 (a,b,c) (page 2)
+Question 11 (b) (page 2)
+Question 12 (b,c) (page 2)
+Source: 15a. Transformations of graphs</t>
+      </text>
+    </comment>
     <comment ref="N44" authorId="0" shapeId="0">
       <text>
         <t>Page 3: the question starting there (d)
@@ -1700,6 +1807,19 @@
 Source: Question Set 4: Graphs and Transformations exam questions</t>
       </text>
     </comment>
+    <comment ref="J46" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 7 (page 2)
+Question 11 (page 2)
+Question 13 (page 2)
+Source: 15a. Transformations of graphs</t>
+      </text>
+    </comment>
     <comment ref="N46" authorId="0" shapeId="0">
       <text>
         <t>Page 9: the question starting there (d)
@@ -1712,6 +1832,14 @@
 Question 35 (b) (page 45)
 Question 36 (b) (page 47)
 Source: Question Set 2: Functions and Graphs exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J47" authorId="0" shapeId="0">
+      <text>
+        <t>Question 3 (page 1)
+Question 4 (a,b,c,d,e,f) (page 1)
+Question 7 (page 1)
+Source: 04a. The modulus function</t>
       </text>
     </comment>
     <comment ref="N47" authorId="0" shapeId="0">
@@ -1826,6 +1954,19 @@
 Question 6 (a) (page 5)
 Question 10 (a) (page 8)
 Source: Question Set 5: Straight Line Graphs exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J54" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 5 (page 1)
+Question 7 (page 1)
+Question 9 (page 1)
+Question 12 (page 2)
+Question 19 (page 2)
+Source: 1a. Equations of straight lines</t>
       </text>
     </comment>
     <comment ref="N54" authorId="0" shapeId="0">
@@ -1955,6 +2096,15 @@
 Source: Question Set 5: Straight Line Graphs exam questions</t>
       </text>
     </comment>
+    <comment ref="J59" authorId="0" shapeId="0">
+      <text>
+        <t>Question 2 (b) (page 1)
+Question 3 (b,c) (page 1)
+Question 5 (b) (page 1)
+Question 7 (b) (page 2)
+Source: 3a. Coordinate geometry − further questions</t>
+      </text>
+    </comment>
     <comment ref="N59" authorId="0" shapeId="0">
       <text>
         <t>Page 8: the question starting there (a)
@@ -2066,6 +2216,13 @@
 Source: Question Set 6: Circles exam questions</t>
       </text>
     </comment>
+    <comment ref="J63" authorId="0" shapeId="0">
+      <text>
+        <t>Question 6 (page 1)
+Question 11 (page 1)
+Source: 4a. Circles</t>
+      </text>
+    </comment>
     <comment ref="G64" authorId="0" shapeId="0">
       <text>
         <t>Question 1 (a) (page 1)
@@ -2124,6 +2281,14 @@
 Question 7 (b) (page 6)
 Question 8 (b) (page 7)
 Source: Question Set 8: Parametric Equations exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J66" authorId="0" shapeId="0">
+      <text>
+        <t>Question 4 (page 1)
+Question 6 (page 1)
+Question 8 (page 1)
+Source: 13a. Parametric equations</t>
       </text>
     </comment>
     <comment ref="N66" authorId="0" shapeId="0">
@@ -2244,6 +2409,15 @@
 Source: Question Set 8: The Binomial Expansion exam questions</t>
       </text>
     </comment>
+    <comment ref="J74" authorId="0" shapeId="0">
+      <text>
+        <t>Question 5 (b) (page 1)
+Question 6 (b) (page 1)
+Question 11 (b) (page 2)
+Question 13 (b) (page 2)
+Source: 2a. Binomial expansions − further questions</t>
+      </text>
+    </comment>
     <comment ref="N74" authorId="0" shapeId="0">
       <text>
         <t>Page 1: the question starting there (c)
@@ -2265,6 +2439,17 @@
 Source: Question Set 4: Binomial Expansion exam questions</t>
       </text>
     </comment>
+    <comment ref="J75" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 6 (page 1)
+Source: 01a. Binomial expansions</t>
+      </text>
+    </comment>
     <comment ref="N75" authorId="0" shapeId="0">
       <text>
         <t>Page 1: the question starting there (a)
@@ -2691,10 +2876,25 @@
 Source: Question Set 10: Trigonometric Identities and Equations exam questions</t>
       </text>
     </comment>
+    <comment ref="J93" authorId="0" shapeId="0">
+      <text>
+        <t>Question 2 (page 1)
+Source: 2a. Trigonometric ratios and graphs</t>
+      </text>
+    </comment>
     <comment ref="G94" authorId="0" shapeId="0">
       <text>
         <t>Question 10 (page 13)
 Source: Question Set 5: Radians exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J94" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Source: 01a. Radians, arcs and sectors</t>
       </text>
     </comment>
     <comment ref="N94" authorId="0" shapeId="0">
@@ -2744,6 +2944,15 @@
 Source: Question Set 5: Radians exam questions</t>
       </text>
     </comment>
+    <comment ref="J96" authorId="0" shapeId="0">
+      <text>
+        <t>Page 7: the question starting there (c,d)
+Page 10: the question starting there (c,d)
+Page 16: the question starting there (c)
+Page 18: the question starting there (b)
+Source: Arc length and Sector area</t>
+      </text>
+    </comment>
     <comment ref="N96" authorId="0" shapeId="0">
       <text>
         <t>Page 7: the question starting there (c)
@@ -2797,11 +3006,29 @@
 Source: Question Set 9: Trigonometric Ratios exam questions</t>
       </text>
     </comment>
+    <comment ref="J99" authorId="0" shapeId="0">
+      <text>
+        <t>Question 7 (page 2)
+Question 8 (page 2)
+Question 9 (page 2)
+Question 10 (page 2)
+Question 11 (page 2)
+Question 12 (page 2)
+Source: 2a. Trigonometric ratios and graphs</t>
+      </text>
+    </comment>
     <comment ref="N99" authorId="0" shapeId="0">
       <text>
         <t>Page 3: the question starting there (a,b)
 Page 11: the question starting there (a)
 Source: Ch10 Trigonometric Identities and Equations Exam Questions</t>
+      </text>
+    </comment>
+    <comment ref="J100" authorId="0" shapeId="0">
+      <text>
+        <t>Question 2 (page 1)
+Question 4 (page 1)
+Source: 2a. Trigonometric ratios and graphs</t>
       </text>
     </comment>
     <comment ref="G101" authorId="0" shapeId="0">
@@ -2815,6 +3042,18 @@
 Source: Question Set 6: Trigonometric Functions exam questions</t>
       </text>
     </comment>
+    <comment ref="J101" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 6 (page 1)
+Question 15 (page 2)
+Source: 04a. Secant, cosecant and cotangent</t>
+      </text>
+    </comment>
     <comment ref="N101" authorId="0" shapeId="0">
       <text>
         <t>Page 6: the question starting there (a)
@@ -2827,10 +3066,31 @@
 Source: Question Set 6: Trigonometric Functions exam questions</t>
       </text>
     </comment>
+    <comment ref="J102" authorId="0" shapeId="0">
+      <text>
+        <t>Question 7 (page 1)
+Question 8 (page 1)
+Question 9 (page 1)
+Source: 04a. Secant, cosecant and cotangent</t>
+      </text>
+    </comment>
     <comment ref="G103" authorId="0" shapeId="0">
       <text>
         <t>Question 20 (page 27)
 Source: Question Set 2: Functions and Graphs exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J103" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 7 (page 1)
+Question 8 (page 1)
+Question 9 (page 1)
+Source: 03a. Inverse trigonometric functions</t>
       </text>
     </comment>
     <comment ref="N103" authorId="0" shapeId="0">
@@ -2884,6 +3144,19 @@
 Source: Question Set 6: Trigonometric Functions exam questions</t>
       </text>
     </comment>
+    <comment ref="J105" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 6 (page 1)
+Question 7 (page 1)
+Question 8 (page 1)
+Source: 05a. Pythagorean identities</t>
+      </text>
+    </comment>
     <comment ref="N105" authorId="0" shapeId="0">
       <text>
         <t>Page 12: the question starting there (a)
@@ -3177,6 +3450,15 @@
 Source: A Level Maths: Exponentials and Logarithms — Medium</t>
       </text>
     </comment>
+    <comment ref="J118" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Source: 3a. Laws of logarithms</t>
+      </text>
+    </comment>
     <comment ref="N118" authorId="0" shapeId="0">
       <text>
         <t>Page 11: the question starting there (b)
@@ -3696,6 +3978,16 @@
 Source: Question Set 9: Differentiation exam questions</t>
       </text>
     </comment>
+    <comment ref="J142" authorId="0" shapeId="0">
+      <text>
+        <t>Question 2 (b,c,d) (page 1)
+Question 3 (page 1)
+Question 5 (b) (page 1)
+Question 6 (d) (page 1)
+Question 14 (page 2)
+Source: 04a. Differentiating trigonometric functions</t>
+      </text>
+    </comment>
     <comment ref="N142" authorId="0" shapeId="0">
       <text>
         <t>Page 2: the question starting there (a, c)
@@ -3998,6 +4290,17 @@
 Source: Question Set 11: Integration exam questions</t>
       </text>
     </comment>
+    <comment ref="J156" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (page 1)
+Question 6 (page 1)
+Source: 03a. Integrating functions of ax + b</t>
+      </text>
+    </comment>
     <comment ref="N156" authorId="0" shapeId="0">
       <text>
         <t>Page 1: the question starting there
@@ -4017,6 +4320,15 @@
 Source: Question Set 11: Integration exam questions</t>
       </text>
     </comment>
+    <comment ref="J157" authorId="0" shapeId="0">
+      <text>
+        <t>Question 3 (page 1)
+Question 4 (page 1)
+Question 5 (a,b,c,e,f,g,h,i) (page 1)
+Question 6 (a,b,c,e,f) (page 1)
+Source: 02a. Integrating trigonometric functions</t>
+      </text>
+    </comment>
     <comment ref="N157" authorId="0" shapeId="0">
       <text>
         <t>Page 14: the question starting there
@@ -4029,6 +4341,14 @@
 Question 45 (b) (page 45)
 Question 63 (page 69)
 Source: Question Set 11: Integration exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J158" authorId="0" shapeId="0">
+      <text>
+        <t>Question 6 (page 2)
+Question 7 (page 2)
+Question 8 (page 2)
+Source: 04a. Integration by substitution</t>
       </text>
     </comment>
     <comment ref="N158" authorId="0" shapeId="0">
@@ -4123,6 +4443,14 @@
 Source: Question Set 11: Integration exam questions</t>
       </text>
     </comment>
+    <comment ref="J162" authorId="0" shapeId="0">
+      <text>
+        <t>Page 5: the question starting there (b)
+Page 8: the question starting there (b)
+Page 11: the question starting there (c)
+Source: Finding Areas using Integration 2</t>
+      </text>
+    </comment>
     <comment ref="N162" authorId="0" shapeId="0">
       <text>
         <t>Page 3: the question starting there
@@ -4374,6 +4702,16 @@
 Source: Ch11 Integration Exam Questions 2</t>
       </text>
     </comment>
+    <comment ref="J176" authorId="0" shapeId="0">
+      <text>
+        <t>Question 1 (page 1)
+Question 2 (page 1)
+Question 7 (page 1)
+Question 9 (a) (page 1)
+Question 10 (a,c,d) (page 1)
+Source: 2a. Cartesian components of a vector</t>
+      </text>
+    </comment>
     <comment ref="G177" authorId="0" shapeId="0">
       <text>
         <t>Question 1 (page 1)
@@ -4554,6 +4892,12 @@
 Question 5 (page 2)
 Question 6 (page 2)
 Source: A Level Maths: Vectors — Medium</t>
+      </text>
+    </comment>
+    <comment ref="J184" authorId="0" shapeId="0">
+      <text>
+        <t>Question 21 (page 2)
+Source: 2a. Cartesian components of a vector</t>
       </text>
     </comment>
   </commentList>
@@ -4573,6 +4917,17 @@
 Source: 1.2 Sampling</t>
       </text>
     </comment>
+    <comment ref="J9" authorId="0" shapeId="0">
+      <text>
+        <t>Page 1: the question starting there (a,c)
+Page 2: the question starting there
+Page 3: the question starting there
+Page 4: the question starting there
+Page 4: the question starting there
+Page 5: the question starting there (a,b,c,d)
+Source: Sampling methods 1</t>
+      </text>
+    </comment>
     <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <t>Page 11: the question starting there (a, b, c)
@@ -4588,6 +4943,19 @@
 Source: 1.2 Sampling</t>
       </text>
     </comment>
+    <comment ref="J10" authorId="0" shapeId="0">
+      <text>
+        <t>Page 1: the question starting there (a,b)
+Page 2: the question starting there (a)
+Page 3: the question starting there (b,c)
+Page 3: the question starting there (b)
+Page 3: the question starting there
+Page 4: the question starting there (a)
+Page 4: the question starting there
+Page 5: the question starting there (a)
+Source: Sampling methods 2</t>
+      </text>
+    </comment>
     <comment ref="N10" authorId="0" shapeId="0">
       <text>
         <t>Page 2: the question starting there (a)
@@ -4600,6 +4968,16 @@
 Question 3 (c, d) (page 3)
 Question 5 (page 5)
 Source: 1.2 Sampling</t>
+      </text>
+    </comment>
+    <comment ref="J11" authorId="0" shapeId="0">
+      <text>
+        <t>Page 2: the question starting there (b)
+Page 3: the question starting there (a)
+Page 3: the question starting there (a)
+Page 4: the question starting there (b)
+Page 5: the question starting there (b)
+Source: Sampling methods 2</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
@@ -4726,6 +5104,19 @@
 Source: Question Set 3: Representations of Data exam questions</t>
       </text>
     </comment>
+    <comment ref="J19" authorId="0" shapeId="0">
+      <text>
+        <t>Page 13: the question starting there (a,b,c)
+Page 19: the question starting there
+Page 24: the question starting there (a,b)
+Page 25: the question starting there (b,c)
+Page 26: the question starting there (b)
+Page 30: the question starting there (d,e)
+Page 32: the question starting there (b)
+Page 33: the question starting there (c)
+Source: Representation and summary data</t>
+      </text>
+    </comment>
     <comment ref="N19" authorId="0" shapeId="0">
       <text>
         <t>Page 2: the question starting there (d)
@@ -5106,6 +5497,16 @@
 Question 6 (page 12)
 Question 8 (page 15)
 Source: Question Set 2: Conditional Probability exam questions</t>
+      </text>
+    </comment>
+    <comment ref="J38" authorId="0" shapeId="0">
+      <text>
+        <t>Page 1: the question starting there (a,b,c)
+Page 4: the question starting there
+Page 8: the question starting there
+Page 11: the question starting there
+Page 19: the question starting there
+Source: Probability</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
@@ -5739,6 +6140,14 @@
 Source: Exam Booklet</t>
       </text>
     </comment>
+    <comment ref="J20" authorId="0" shapeId="0">
+      <text>
+        <t>Page 1: the question starting there
+Page 1: the question starting there (a)
+Page 2: the question starting there (a)
+Source: Kinematics - Problems with calculus</t>
+      </text>
+    </comment>
     <comment ref="N20" authorId="0" shapeId="0">
       <text>
         <t>Page 1: the question starting there (c)
@@ -5776,6 +6185,12 @@
 Source: Ch8 Further Kinematics Exam Questions 1</t>
       </text>
     </comment>
+    <comment ref="J22" authorId="0" shapeId="0">
+      <text>
+        <t>Page 1: the question starting there
+Source: Kinematics - by Graphical Methods</t>
+      </text>
+    </comment>
     <comment ref="N22" authorId="0" shapeId="0">
       <text>
         <t>Page 1: the question starting there
@@ -5845,6 +6260,12 @@
 Source: Ch8 Further Kinematics Exam Questions 1</t>
       </text>
     </comment>
+    <comment ref="J25" authorId="0" shapeId="0">
+      <text>
+        <t>Page 9: the question starting there (a)
+Source: Kinematics - Projectiles 2</t>
+      </text>
+    </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
         <t>Page 6: the question starting there (b,c)
@@ -6277,6 +6698,13 @@
 Source: A Level Maths: Moments — Medium</t>
       </text>
     </comment>
+    <comment ref="J48" authorId="0" shapeId="0">
+      <text>
+        <t>Page 5: the question starting there (c)
+Page 9: the question starting there
+Source: Moments - Moments about a point 1</t>
+      </text>
+    </comment>
     <comment ref="N48" authorId="0" shapeId="0">
       <text>
         <t>Page 7: the question starting there
@@ -6289,6 +6717,15 @@
       <text>
         <t>Question 5 (b,c) (page 4)
 Source: A Level Maths: Moments — Medium</t>
+      </text>
+    </comment>
+    <comment ref="J49" authorId="0" shapeId="0">
+      <text>
+        <t>Page 3: the question starting there (b,c)
+Page 6: the question starting there (b)
+Page 7: the question starting there (c)
+Page 10: the question starting there (a,b)
+Source: Moments - Moments about a point 1</t>
       </text>
     </comment>
     <comment ref="N49" authorId="0" shapeId="0">
@@ -6889,7 +7326,7 @@
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>Real past-paper questions collected by Physics &amp; Maths Tutor, with the mark scheme and model answers.</t>
+          <t>Physics &amp; Maths Tutor sheets: Edexcel past-paper questions (with mark scheme and model answers), or a Solomon topic worksheet (with answers) where that covers the topic better. Set A sheets have the mark scheme at the back of the same PDF.</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7635,7 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="20" customHeight="1">
+    <row r="10" outlineLevel="1" ht="32" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>P1.1</t>
@@ -7229,18 +7666,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I10" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J10" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="39" t="n"/>
+      <c r="I10" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Mixed exam-style questions on proof</t>
+        </is>
+      </c>
+      <c r="J10" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 3, 7 +1</t>
+        </is>
+      </c>
+      <c r="K10" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L10" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M10" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch7</t>
@@ -7273,7 +7718,7 @@
           <t>Proof by contradiction (incl. √2 irrational, infinitely many primes)</t>
         </is>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="C11" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="34" t="n"/>
@@ -7467,18 +7912,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I15" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J15" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K15" s="39" t="n"/>
-      <c r="L15" s="39" t="n"/>
+      <c r="I15" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Indices</t>
+        </is>
+      </c>
+      <c r="J15" s="36" t="inlineStr">
+        <is>
+          <t>Q 4, 5, 6 +5</t>
+        </is>
+      </c>
+      <c r="K15" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L15" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M15" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch1</t>
@@ -7531,18 +7984,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I16" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J16" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K16" s="39" t="n"/>
-      <c r="L16" s="39" t="n"/>
+      <c r="I16" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Surds</t>
+        </is>
+      </c>
+      <c r="J16" s="36" t="inlineStr">
+        <is>
+          <t>Q 4, 5, 7 +5</t>
+        </is>
+      </c>
+      <c r="K16" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L16" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M16" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch1</t>
@@ -7620,12 +8081,12 @@
           <t>Pure 1 Ch2</t>
         </is>
       </c>
-      <c r="N17" s="38" t="inlineStr">
+      <c r="N17" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O17" s="41" t="n"/>
+      <c r="O17" s="39" t="n"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>P2</t>
@@ -7920,7 +8381,7 @@
         </is>
       </c>
     </row>
-    <row r="22" outlineLevel="1" ht="20" customHeight="1">
+    <row r="22" outlineLevel="1" ht="32" customHeight="1">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>P2.4</t>
@@ -7941,42 +8402,50 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G22" s="38" t="inlineStr">
+      <c r="G22" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H22" s="39" t="n"/>
-      <c r="I22" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J22" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K22" s="39" t="n"/>
-      <c r="L22" s="39" t="n"/>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Simultaneous equations</t>
+        </is>
+      </c>
+      <c r="J22" s="36" t="inlineStr">
+        <is>
+          <t>Q 1</t>
+        </is>
+      </c>
+      <c r="K22" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L22" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M22" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch3</t>
         </is>
       </c>
-      <c r="N22" s="38" t="inlineStr">
+      <c r="N22" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O22" s="41" t="n"/>
+      <c r="O22" s="39" t="n"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
     </row>
-    <row r="23" outlineLevel="1" ht="20" customHeight="1">
+    <row r="23" outlineLevel="1" ht="32" customHeight="1">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>P2.4</t>
@@ -8007,18 +8476,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I23" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J23" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K23" s="39" t="n"/>
-      <c r="L23" s="39" t="n"/>
+      <c r="I23" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Simultaneous equations</t>
+        </is>
+      </c>
+      <c r="J23" s="36" t="inlineStr">
+        <is>
+          <t>Q 2, 3, 4 +1</t>
+        </is>
+      </c>
+      <c r="K23" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L23" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M23" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch3</t>
@@ -8071,18 +8548,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I24" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J24" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K24" s="39" t="n"/>
-      <c r="L24" s="39" t="n"/>
+      <c r="I24" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Inequalities</t>
+        </is>
+      </c>
+      <c r="J24" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2</t>
+        </is>
+      </c>
+      <c r="K24" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L24" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M24" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch3</t>
@@ -8197,12 +8682,12 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G26" s="38" t="inlineStr">
+      <c r="G26" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H26" s="39" t="n"/>
+      <c r="H26" s="40" t="n"/>
       <c r="I26" s="35" t="inlineStr">
         <is>
           <t>Inequalities</t>
@@ -8275,29 +8760,37 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I27" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J27" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K27" s="39" t="n"/>
-      <c r="L27" s="39" t="n"/>
+      <c r="I27" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Polynomials</t>
+        </is>
+      </c>
+      <c r="J27" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +3</t>
+        </is>
+      </c>
+      <c r="K27" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L27" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M27" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch1</t>
         </is>
       </c>
-      <c r="N27" s="38" t="inlineStr">
+      <c r="N27" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O27" s="41" t="n"/>
+      <c r="O27" s="39" t="n"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>P2</t>
@@ -8387,7 +8880,7 @@
           <t>Simplifying algebraic fractions (factorising and cancelling)</t>
         </is>
       </c>
-      <c r="C29" s="40" t="n">
+      <c r="C29" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="34" t="n"/>
@@ -8397,35 +8890,43 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G29" s="38" t="inlineStr">
+      <c r="G29" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H29" s="39" t="n"/>
-      <c r="I29" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J29" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K29" s="39" t="n"/>
-      <c r="L29" s="39" t="n"/>
+      <c r="H29" s="40" t="n"/>
+      <c r="I29" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Rational expressions (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J29" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 4</t>
+        </is>
+      </c>
+      <c r="K29" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L29" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M29" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch7</t>
         </is>
       </c>
-      <c r="N29" s="38" t="inlineStr">
+      <c r="N29" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O29" s="41" t="n"/>
+      <c r="O29" s="39" t="n"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>P2</t>
@@ -8587,7 +9088,7 @@
           <t>Adding, subtracting, multiplying and dividing algebraic fractions</t>
         </is>
       </c>
-      <c r="C32" s="40" t="n">
+      <c r="C32" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="34" t="n"/>
@@ -8607,18 +9108,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I32" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J32" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K32" s="39" t="n"/>
-      <c r="L32" s="39" t="n"/>
+      <c r="I32" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Rational expressions (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J32" s="36" t="inlineStr">
+        <is>
+          <t>Q 2, 3, 5 +5</t>
+        </is>
+      </c>
+      <c r="K32" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L32" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M32" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch1</t>
@@ -8651,7 +9160,7 @@
           <t>Algebraic division of improper fractions</t>
         </is>
       </c>
-      <c r="C33" s="40" t="n">
+      <c r="C33" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="34" t="n"/>
@@ -8805,35 +9314,43 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G35" s="38" t="inlineStr">
+      <c r="G35" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H35" s="39" t="n"/>
-      <c r="I35" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J35" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K35" s="39" t="n"/>
-      <c r="L35" s="39" t="n"/>
+      <c r="H35" s="40" t="n"/>
+      <c r="I35" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Graphs of functions</t>
+        </is>
+      </c>
+      <c r="J35" s="36" t="inlineStr">
+        <is>
+          <t>Q 1</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L35" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M35" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch4</t>
         </is>
       </c>
-      <c r="N35" s="38" t="inlineStr">
+      <c r="N35" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O35" s="41" t="n"/>
+      <c r="O35" s="39" t="n"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>P2</t>
@@ -9005,35 +9522,35 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G38" s="38" t="inlineStr">
+      <c r="G38" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H38" s="39" t="n"/>
-      <c r="I38" s="37" t="inlineStr">
+      <c r="H38" s="40" t="n"/>
+      <c r="I38" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J38" s="38" t="inlineStr">
+      <c r="J38" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K38" s="39" t="n"/>
-      <c r="L38" s="39" t="n"/>
+      <c r="K38" s="40" t="n"/>
+      <c r="L38" s="40" t="n"/>
       <c r="M38" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch4</t>
         </is>
       </c>
-      <c r="N38" s="38" t="inlineStr">
+      <c r="N38" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O38" s="41" t="n"/>
+      <c r="O38" s="39" t="n"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>P2</t>
@@ -9051,7 +9568,7 @@
           <t>The modulus function and its graph y = |ax + b|</t>
         </is>
       </c>
-      <c r="C39" s="40" t="n">
+      <c r="C39" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="34" t="n"/>
@@ -9123,7 +9640,7 @@
           <t>Solving modulus equations and inequalities</t>
         </is>
       </c>
-      <c r="C40" s="40" t="n">
+      <c r="C40" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="34" t="n"/>
@@ -9195,7 +9712,7 @@
           <t>Functions and mappings: domain and range</t>
         </is>
       </c>
-      <c r="C41" s="40" t="n">
+      <c r="C41" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="34" t="n"/>
@@ -9267,7 +9784,7 @@
           <t>Composite functions</t>
         </is>
       </c>
-      <c r="C42" s="40" t="n">
+      <c r="C42" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="34" t="n"/>
@@ -9339,7 +9856,7 @@
           <t>Inverse functions and their graphs</t>
         </is>
       </c>
-      <c r="C43" s="40" t="n">
+      <c r="C43" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="34" t="n"/>
@@ -9400,7 +9917,7 @@
         </is>
       </c>
     </row>
-    <row r="44" outlineLevel="1" ht="20" customHeight="1">
+    <row r="44" outlineLevel="1" ht="32" customHeight="1">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>P2.9</t>
@@ -9431,18 +9948,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I44" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J44" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K44" s="39" t="n"/>
-      <c r="L44" s="39" t="n"/>
+      <c r="I44" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Transformations of graphs</t>
+        </is>
+      </c>
+      <c r="J44" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +5</t>
+        </is>
+      </c>
+      <c r="K44" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L44" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M44" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch4</t>
@@ -9567,18 +10092,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I46" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J46" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K46" s="39" t="n"/>
-      <c r="L46" s="39" t="n"/>
+      <c r="I46" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Transformations of graphs</t>
+        </is>
+      </c>
+      <c r="J46" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +5</t>
+        </is>
+      </c>
+      <c r="K46" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L46" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M46" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch4</t>
@@ -9600,7 +10133,7 @@
         </is>
       </c>
     </row>
-    <row r="47" outlineLevel="1" ht="20" customHeight="1">
+    <row r="47" outlineLevel="1" ht="32" customHeight="1">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>P2.9</t>
@@ -9611,7 +10144,7 @@
           <t>y = |f(x)| and y = f(|x|)</t>
         </is>
       </c>
-      <c r="C47" s="40" t="n">
+      <c r="C47" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D47" s="34" t="n"/>
@@ -9631,18 +10164,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I47" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J47" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K47" s="39" t="n"/>
-      <c r="L47" s="39" t="n"/>
+      <c r="I47" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: The modulus function (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J47" s="36" t="inlineStr">
+        <is>
+          <t>Q 3, 4, 7</t>
+        </is>
+      </c>
+      <c r="K47" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L47" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M47" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch2</t>
@@ -9675,7 +10216,7 @@
           <t>Combining transformations</t>
         </is>
       </c>
-      <c r="C48" s="40" t="n">
+      <c r="C48" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="34" t="n"/>
@@ -9747,7 +10288,7 @@
           <t>Partial fractions (distinct linear factors)</t>
         </is>
       </c>
-      <c r="C49" s="40" t="n">
+      <c r="C49" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D49" s="34" t="n"/>
@@ -9819,7 +10360,7 @@
           <t>Partial fractions with repeated factors</t>
         </is>
       </c>
-      <c r="C50" s="40" t="n">
+      <c r="C50" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D50" s="34" t="n"/>
@@ -9891,7 +10432,7 @@
           <t>Using functions in modelling (limitations and refinements)</t>
         </is>
       </c>
-      <c r="C51" s="40" t="n">
+      <c r="C51" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D51" s="34" t="n"/>
@@ -9982,7 +10523,7 @@
       <c r="N53" s="29" t="n"/>
       <c r="O53" s="29" t="n"/>
     </row>
-    <row r="54" outlineLevel="1" ht="20" customHeight="1">
+    <row r="54" outlineLevel="1" ht="32" customHeight="1">
       <c r="A54" s="31" t="inlineStr">
         <is>
           <t>P3.1</t>
@@ -10013,18 +10554,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I54" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J54" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K54" s="39" t="n"/>
-      <c r="L54" s="39" t="n"/>
+      <c r="I54" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Equations of straight lines</t>
+        </is>
+      </c>
+      <c r="J54" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +5</t>
+        </is>
+      </c>
+      <c r="K54" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L54" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M54" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch5</t>
@@ -10334,7 +10883,7 @@
         </is>
       </c>
     </row>
-    <row r="59" outlineLevel="1" ht="20" customHeight="1">
+    <row r="59" outlineLevel="1" ht="32" customHeight="1">
       <c r="A59" s="31" t="inlineStr">
         <is>
           <t>P3.2</t>
@@ -10365,18 +10914,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I59" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J59" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K59" s="39" t="n"/>
-      <c r="L59" s="39" t="n"/>
+      <c r="I59" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Coordinate geometry – further questions</t>
+        </is>
+      </c>
+      <c r="J59" s="36" t="inlineStr">
+        <is>
+          <t>Q 2, 3, 5 +1</t>
+        </is>
+      </c>
+      <c r="K59" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L59" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M59" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch6</t>
@@ -10645,29 +11202,37 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I63" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J63" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K63" s="39" t="n"/>
-      <c r="L63" s="39" t="n"/>
+      <c r="I63" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Circles</t>
+        </is>
+      </c>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>Q 6, 11</t>
+        </is>
+      </c>
+      <c r="K63" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L63" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M63" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch6</t>
         </is>
       </c>
-      <c r="N63" s="38" t="inlineStr">
+      <c r="N63" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O63" s="41" t="n"/>
+      <c r="O63" s="39" t="n"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>P3</t>
@@ -10685,7 +11250,7 @@
           <t>Parametric equations: converting to Cartesian form</t>
         </is>
       </c>
-      <c r="C64" s="40" t="n">
+      <c r="C64" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D64" s="34" t="n"/>
@@ -10757,7 +11322,7 @@
           <t>Parametric equations using trig identities</t>
         </is>
       </c>
-      <c r="C65" s="40" t="n">
+      <c r="C65" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D65" s="34" t="n"/>
@@ -10818,7 +11383,7 @@
         </is>
       </c>
     </row>
-    <row r="66" outlineLevel="1" ht="20" customHeight="1">
+    <row r="66" outlineLevel="1" ht="32" customHeight="1">
       <c r="A66" s="31" t="inlineStr">
         <is>
           <t>P3.3</t>
@@ -10829,7 +11394,7 @@
           <t>Sketching parametric curves</t>
         </is>
       </c>
-      <c r="C66" s="40" t="n">
+      <c r="C66" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D66" s="34" t="n"/>
@@ -10849,18 +11414,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I66" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J66" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K66" s="39" t="n"/>
-      <c r="L66" s="39" t="n"/>
+      <c r="I66" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Parametric equations (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J66" s="36" t="inlineStr">
+        <is>
+          <t>Q 4, 6, 8</t>
+        </is>
+      </c>
+      <c r="K66" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L66" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M66" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch8</t>
@@ -10893,7 +11466,7 @@
           <t>Points of intersection with parametric curves</t>
         </is>
       </c>
-      <c r="C67" s="40" t="n">
+      <c r="C67" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D67" s="34" t="n"/>
@@ -10965,7 +11538,7 @@
           <t>Modelling with parametric equations</t>
         </is>
       </c>
-      <c r="C68" s="40" t="n">
+      <c r="C68" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D68" s="34" t="n"/>
@@ -10975,24 +11548,24 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G68" s="38" t="inlineStr">
+      <c r="G68" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H68" s="39" t="n"/>
-      <c r="I68" s="37" t="inlineStr">
+      <c r="H68" s="40" t="n"/>
+      <c r="I68" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J68" s="38" t="inlineStr">
+      <c r="J68" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K68" s="39" t="n"/>
-      <c r="L68" s="39" t="n"/>
+      <c r="K68" s="40" t="n"/>
+      <c r="L68" s="40" t="n"/>
       <c r="M68" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch8</t>
@@ -11075,29 +11648,29 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I71" s="37" t="inlineStr">
+      <c r="I71" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J71" s="38" t="inlineStr">
+      <c r="J71" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K71" s="39" t="n"/>
-      <c r="L71" s="39" t="n"/>
+      <c r="K71" s="40" t="n"/>
+      <c r="L71" s="40" t="n"/>
       <c r="M71" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch8</t>
         </is>
       </c>
-      <c r="N71" s="38" t="inlineStr">
+      <c r="N71" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O71" s="41" t="n"/>
+      <c r="O71" s="39" t="n"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>P4</t>
@@ -11248,7 +11821,7 @@
         </is>
       </c>
     </row>
-    <row r="74" outlineLevel="1" ht="20" customHeight="1">
+    <row r="74" outlineLevel="1" ht="32" customHeight="1">
       <c r="A74" s="31" t="inlineStr">
         <is>
           <t>P4.1</t>
@@ -11279,18 +11852,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I74" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J74" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K74" s="39" t="n"/>
-      <c r="L74" s="39" t="n"/>
+      <c r="I74" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Binomial expansions – further questions</t>
+        </is>
+      </c>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>Q 5, 6, 11 +1</t>
+        </is>
+      </c>
+      <c r="K74" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L74" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M74" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch8</t>
@@ -11301,7 +11882,7 @@
           <t>pp 1, 3, 7</t>
         </is>
       </c>
-      <c r="O74" s="38" t="inlineStr">
+      <c r="O74" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -11323,7 +11904,7 @@
           <t>Binomial expansion of (1 + x)ⁿ for rational n, and validity</t>
         </is>
       </c>
-      <c r="C75" s="40" t="n">
+      <c r="C75" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D75" s="34" t="n"/>
@@ -11343,18 +11924,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I75" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J75" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K75" s="39" t="n"/>
-      <c r="L75" s="39" t="n"/>
+      <c r="I75" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Binomial expansions (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +3</t>
+        </is>
+      </c>
+      <c r="K75" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L75" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M75" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch4</t>
@@ -11365,7 +11954,7 @@
           <t>pp 1, 7, 10</t>
         </is>
       </c>
-      <c r="O75" s="38" t="inlineStr">
+      <c r="O75" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -11387,7 +11976,7 @@
           <t>Binomial expansion of (a + bx)ⁿ for rational n</t>
         </is>
       </c>
-      <c r="C76" s="40" t="n">
+      <c r="C76" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D76" s="34" t="n"/>
@@ -11437,7 +12026,7 @@
           <t>pp 2, 3, 5 +4</t>
         </is>
       </c>
-      <c r="O76" s="38" t="inlineStr">
+      <c r="O76" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -11459,7 +12048,7 @@
           <t>Binomial expansion using partial fractions</t>
         </is>
       </c>
-      <c r="C77" s="40" t="n">
+      <c r="C77" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D77" s="34" t="n"/>
@@ -11469,12 +12058,12 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G77" s="38" t="inlineStr">
+      <c r="G77" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H77" s="39" t="n"/>
+      <c r="H77" s="40" t="n"/>
       <c r="I77" s="35" t="inlineStr">
         <is>
           <t>Binomial Expansion (Yr 2)</t>
@@ -11505,7 +12094,7 @@
           <t>pp 8, 11</t>
         </is>
       </c>
-      <c r="O77" s="38" t="inlineStr">
+      <c r="O77" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -11527,7 +12116,7 @@
           <t>Recurrence relations uₙ₊₁ = f(uₙ)</t>
         </is>
       </c>
-      <c r="C78" s="40" t="n">
+      <c r="C78" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D78" s="34" t="n"/>
@@ -11599,7 +12188,7 @@
           <t>Increasing, decreasing and periodic sequences</t>
         </is>
       </c>
-      <c r="C79" s="40" t="n">
+      <c r="C79" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D79" s="34" t="n"/>
@@ -11671,7 +12260,7 @@
           <t>Sigma notation</t>
         </is>
       </c>
-      <c r="C80" s="40" t="n">
+      <c r="C80" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D80" s="34" t="n"/>
@@ -11743,7 +12332,7 @@
           <t>Arithmetic sequences</t>
         </is>
       </c>
-      <c r="C81" s="40" t="n">
+      <c r="C81" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D81" s="34" t="n"/>
@@ -11815,7 +12404,7 @@
           <t>Arithmetic series (incl. proof of the sum formula)</t>
         </is>
       </c>
-      <c r="C82" s="40" t="n">
+      <c r="C82" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D82" s="34" t="n"/>
@@ -11887,7 +12476,7 @@
           <t>Geometric sequences</t>
         </is>
       </c>
-      <c r="C83" s="40" t="n">
+      <c r="C83" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D83" s="34" t="n"/>
@@ -11959,7 +12548,7 @@
           <t>Geometric series (incl. proof of the sum formula, using logs to find n)</t>
         </is>
       </c>
-      <c r="C84" s="40" t="n">
+      <c r="C84" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D84" s="34" t="n"/>
@@ -12031,7 +12620,7 @@
           <t>Sum to infinity and convergence (|r| &lt; 1)</t>
         </is>
       </c>
-      <c r="C85" s="40" t="n">
+      <c r="C85" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D85" s="34" t="n"/>
@@ -12103,7 +12692,7 @@
           <t>Modelling with sequences and series</t>
         </is>
       </c>
-      <c r="C86" s="40" t="n">
+      <c r="C86" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D86" s="34" t="n"/>
@@ -12513,36 +13102,44 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I93" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J93" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K93" s="39" t="n"/>
-      <c r="L93" s="39" t="n"/>
+      <c r="I93" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Trigonometric ratios and graphs</t>
+        </is>
+      </c>
+      <c r="J93" s="36" t="inlineStr">
+        <is>
+          <t>Q 2</t>
+        </is>
+      </c>
+      <c r="K93" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L93" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M93" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch10</t>
         </is>
       </c>
-      <c r="N93" s="38" t="inlineStr">
+      <c r="N93" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O93" s="41" t="n"/>
+      <c r="O93" s="39" t="n"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
     </row>
-    <row r="94" outlineLevel="1" ht="20" customHeight="1">
+    <row r="94" outlineLevel="1" ht="32" customHeight="1">
       <c r="A94" s="31" t="inlineStr">
         <is>
           <t>P5.1</t>
@@ -12553,7 +13150,7 @@
           <t>Radian measure</t>
         </is>
       </c>
-      <c r="C94" s="40" t="n">
+      <c r="C94" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D94" s="34" t="n"/>
@@ -12573,18 +13170,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I94" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J94" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K94" s="39" t="n"/>
-      <c r="L94" s="39" t="n"/>
+      <c r="I94" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Radians, arcs and sectors (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J94" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +1</t>
+        </is>
+      </c>
+      <c r="K94" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L94" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M94" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch5</t>
@@ -12617,7 +13222,7 @@
           <t>Arc length and sector area</t>
         </is>
       </c>
-      <c r="C95" s="40" t="n">
+      <c r="C95" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D95" s="34" t="n"/>
@@ -12678,7 +13283,7 @@
         </is>
       </c>
     </row>
-    <row r="96" outlineLevel="1" ht="20" customHeight="1">
+    <row r="96" outlineLevel="1" ht="32" customHeight="1">
       <c r="A96" s="31" t="inlineStr">
         <is>
           <t>P5.1</t>
@@ -12689,7 +13294,7 @@
           <t>Areas of segments</t>
         </is>
       </c>
-      <c r="C96" s="40" t="n">
+      <c r="C96" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D96" s="34" t="n"/>
@@ -12709,18 +13314,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I96" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J96" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K96" s="39" t="n"/>
-      <c r="L96" s="39" t="n"/>
+      <c r="I96" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Arc length and Sector area (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J96" s="36" t="inlineStr">
+        <is>
+          <t>pp 7, 10, 16 +1</t>
+        </is>
+      </c>
+      <c r="K96" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L96" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M96" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch5</t>
@@ -12753,7 +13366,7 @@
           <t>Small angle approximations</t>
         </is>
       </c>
-      <c r="C97" s="40" t="n">
+      <c r="C97" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D97" s="34" t="n"/>
@@ -12870,19 +13483,19 @@
           <t>Pure 1 Ch9</t>
         </is>
       </c>
-      <c r="N98" s="38" t="inlineStr">
+      <c r="N98" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O98" s="41" t="n"/>
+      <c r="O98" s="39" t="n"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
     </row>
-    <row r="99" outlineLevel="1" ht="20" customHeight="1">
+    <row r="99" outlineLevel="1" ht="32" customHeight="1">
       <c r="A99" s="31" t="inlineStr">
         <is>
           <t>P5.3</t>
@@ -12913,18 +13526,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I99" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J99" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K99" s="39" t="n"/>
-      <c r="L99" s="39" t="n"/>
+      <c r="I99" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Trigonometric ratios and graphs</t>
+        </is>
+      </c>
+      <c r="J99" s="36" t="inlineStr">
+        <is>
+          <t>Q 7, 8, 9 +3</t>
+        </is>
+      </c>
+      <c r="K99" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L99" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M99" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch9</t>
@@ -12946,7 +13567,7 @@
         </is>
       </c>
     </row>
-    <row r="100" outlineLevel="1" ht="20" customHeight="1">
+    <row r="100" outlineLevel="1" ht="32" customHeight="1">
       <c r="A100" s="31" t="inlineStr">
         <is>
           <t>P5.3</t>
@@ -12957,7 +13578,7 @@
           <t>Exact values of sin, cos and tan (degrees and radians)</t>
         </is>
       </c>
-      <c r="C100" s="40" t="n">
+      <c r="C100" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D100" s="34" t="n"/>
@@ -12967,42 +13588,50 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G100" s="38" t="inlineStr">
+      <c r="G100" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H100" s="39" t="n"/>
-      <c r="I100" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J100" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K100" s="39" t="n"/>
-      <c r="L100" s="39" t="n"/>
+      <c r="H100" s="40" t="n"/>
+      <c r="I100" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Trigonometric ratios and graphs</t>
+        </is>
+      </c>
+      <c r="J100" s="36" t="inlineStr">
+        <is>
+          <t>Q 2, 4</t>
+        </is>
+      </c>
+      <c r="K100" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L100" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M100" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch10</t>
         </is>
       </c>
-      <c r="N100" s="38" t="inlineStr">
+      <c r="N100" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O100" s="41" t="n"/>
+      <c r="O100" s="39" t="n"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
     </row>
-    <row r="101" outlineLevel="1" ht="20" customHeight="1">
+    <row r="101" outlineLevel="1" ht="32" customHeight="1">
       <c r="A101" s="31" t="inlineStr">
         <is>
           <t>P5.4</t>
@@ -13013,7 +13642,7 @@
           <t>Sec, cosec and cot: definitions and exact values</t>
         </is>
       </c>
-      <c r="C101" s="40" t="n">
+      <c r="C101" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D101" s="34" t="n"/>
@@ -13033,18 +13662,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I101" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J101" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K101" s="39" t="n"/>
-      <c r="L101" s="39" t="n"/>
+      <c r="I101" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Secant, cosecant and cotangent (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J101" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +4</t>
+        </is>
+      </c>
+      <c r="K101" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L101" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M101" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch6</t>
@@ -13066,7 +13703,7 @@
         </is>
       </c>
     </row>
-    <row r="102" outlineLevel="1" ht="20" customHeight="1">
+    <row r="102" outlineLevel="1" ht="32" customHeight="1">
       <c r="A102" s="31" t="inlineStr">
         <is>
           <t>P5.4</t>
@@ -13077,7 +13714,7 @@
           <t>Graphs of sec x, cosec x and cot x</t>
         </is>
       </c>
-      <c r="C102" s="40" t="n">
+      <c r="C102" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D102" s="34" t="n"/>
@@ -13097,29 +13734,37 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I102" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J102" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K102" s="39" t="n"/>
-      <c r="L102" s="39" t="n"/>
+      <c r="I102" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Secant, cosecant and cotangent (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J102" s="36" t="inlineStr">
+        <is>
+          <t>Q 7, 8, 9</t>
+        </is>
+      </c>
+      <c r="K102" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L102" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M102" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch6</t>
         </is>
       </c>
-      <c r="N102" s="38" t="inlineStr">
+      <c r="N102" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O102" s="41" t="n"/>
+      <c r="O102" s="39" t="n"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>P5</t>
@@ -13137,7 +13782,7 @@
           <t>Inverse trig functions: arcsin, arccos, arctan (domain, range, graphs)</t>
         </is>
       </c>
-      <c r="C103" s="40" t="n">
+      <c r="C103" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D103" s="34" t="n"/>
@@ -13157,18 +13802,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I103" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J103" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K103" s="39" t="n"/>
-      <c r="L103" s="39" t="n"/>
+      <c r="I103" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Inverse trigonometric functions (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J103" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +5</t>
+        </is>
+      </c>
+      <c r="K103" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L103" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M103" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch6</t>
@@ -13262,7 +13915,7 @@
         </is>
       </c>
     </row>
-    <row r="105" outlineLevel="1" ht="20" customHeight="1">
+    <row r="105" outlineLevel="1" ht="32" customHeight="1">
       <c r="A105" s="31" t="inlineStr">
         <is>
           <t>P5.5</t>
@@ -13273,7 +13926,7 @@
           <t>Identities sec²θ = 1 + tan²θ and cosec²θ = 1 + cot²θ</t>
         </is>
       </c>
-      <c r="C105" s="40" t="n">
+      <c r="C105" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D105" s="34" t="n"/>
@@ -13293,18 +13946,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I105" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J105" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K105" s="39" t="n"/>
-      <c r="L105" s="39" t="n"/>
+      <c r="I105" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Pythagorean identities (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J105" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +5</t>
+        </is>
+      </c>
+      <c r="K105" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L105" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M105" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch6</t>
@@ -13337,7 +13998,7 @@
           <t>Addition formulae: sin(A ± B), cos(A ± B), tan(A ± B) and their geometric proofs</t>
         </is>
       </c>
-      <c r="C106" s="40" t="n">
+      <c r="C106" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D106" s="34" t="n"/>
@@ -13409,7 +14070,7 @@
           <t>Double angle formulae (incl. half angles)</t>
         </is>
       </c>
-      <c r="C107" s="40" t="n">
+      <c r="C107" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D107" s="34" t="n"/>
@@ -13481,7 +14142,7 @@
           <t>a cos θ + b sin θ in the form R cos(θ ± α) or R sin(θ ± α)</t>
         </is>
       </c>
-      <c r="C108" s="40" t="n">
+      <c r="C108" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D108" s="34" t="n"/>
@@ -13697,7 +14358,7 @@
           <t>Trig equations in radians, with sec/cosec/cot and compound angles</t>
         </is>
       </c>
-      <c r="C111" s="40" t="n">
+      <c r="C111" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D111" s="34" t="n"/>
@@ -13769,7 +14430,7 @@
           <t>Proving trig identities (reciprocal, addition and double angle)</t>
         </is>
       </c>
-      <c r="C112" s="40" t="n">
+      <c r="C112" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D112" s="34" t="n"/>
@@ -13841,7 +14502,7 @@
           <t>Modelling with trig functions</t>
         </is>
       </c>
-      <c r="C113" s="40" t="n">
+      <c r="C113" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D113" s="34" t="n"/>
@@ -13953,12 +14614,12 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G116" s="38" t="inlineStr">
+      <c r="G116" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H116" s="39" t="n"/>
+      <c r="H116" s="40" t="n"/>
       <c r="I116" s="35" t="inlineStr">
         <is>
           <t>Laws of Logarithms</t>
@@ -13984,12 +14645,12 @@
           <t>Pure 1 Ch14</t>
         </is>
       </c>
-      <c r="N116" s="38" t="inlineStr">
+      <c r="N116" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O116" s="41" t="n"/>
+      <c r="O116" s="39" t="n"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>P6</t>
@@ -14099,18 +14760,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I118" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J118" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K118" s="39" t="n"/>
-      <c r="L118" s="39" t="n"/>
+      <c r="I118" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Laws of logarithms</t>
+        </is>
+      </c>
+      <c r="J118" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +1</t>
+        </is>
+      </c>
+      <c r="K118" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L118" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M118" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch14</t>
@@ -14677,7 +15346,7 @@
           <t>Differentiation from first principles (sin x and cos x)</t>
         </is>
       </c>
-      <c r="C128" s="40" t="n">
+      <c r="C128" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D128" s="34" t="n"/>
@@ -14759,35 +15428,35 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G129" s="38" t="inlineStr">
+      <c r="G129" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H129" s="39" t="n"/>
-      <c r="I129" s="37" t="inlineStr">
+      <c r="H129" s="40" t="n"/>
+      <c r="I129" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J129" s="38" t="inlineStr">
+      <c r="J129" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K129" s="39" t="n"/>
-      <c r="L129" s="39" t="n"/>
+      <c r="K129" s="40" t="n"/>
+      <c r="L129" s="40" t="n"/>
       <c r="M129" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch12</t>
         </is>
       </c>
-      <c r="N129" s="38" t="inlineStr">
+      <c r="N129" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O129" s="41" t="n"/>
+      <c r="O129" s="39" t="n"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>P7</t>
@@ -14877,7 +15546,7 @@
           <t>Concave and convex curves; points of inflection</t>
         </is>
       </c>
-      <c r="C131" s="40" t="n">
+      <c r="C131" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D131" s="34" t="n"/>
@@ -15021,7 +15690,7 @@
           <t>Differentiating sin kx, cos kx and tan kx</t>
         </is>
       </c>
-      <c r="C133" s="40" t="n">
+      <c r="C133" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D133" s="34" t="n"/>
@@ -15093,7 +15762,7 @@
           <t>Differentiating eᵏˣ, aᵏˣ and ln x</t>
         </is>
       </c>
-      <c r="C134" s="40" t="n">
+      <c r="C134" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D134" s="34" t="n"/>
@@ -15453,7 +16122,7 @@
           <t>The chain rule</t>
         </is>
       </c>
-      <c r="C139" s="40" t="n">
+      <c r="C139" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D139" s="34" t="n"/>
@@ -15525,7 +16194,7 @@
           <t>The product rule</t>
         </is>
       </c>
-      <c r="C140" s="40" t="n">
+      <c r="C140" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D140" s="34" t="n"/>
@@ -15597,7 +16266,7 @@
           <t>The quotient rule</t>
         </is>
       </c>
-      <c r="C141" s="40" t="n">
+      <c r="C141" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D141" s="34" t="n"/>
@@ -15669,7 +16338,7 @@
           <t>Differentiating sec, cosec, cot and x = f(y) (dy/dx = 1 ÷ dx/dy)</t>
         </is>
       </c>
-      <c r="C142" s="40" t="n">
+      <c r="C142" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D142" s="34" t="n"/>
@@ -15689,18 +16358,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I142" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J142" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K142" s="39" t="n"/>
-      <c r="L142" s="39" t="n"/>
+      <c r="I142" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Differentiating trigonometric functions (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J142" s="36" t="inlineStr">
+        <is>
+          <t>Q 2, 3, 5 +2</t>
+        </is>
+      </c>
+      <c r="K142" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L142" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M142" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch9</t>
@@ -15733,7 +16410,7 @@
           <t>Connected rates of change</t>
         </is>
       </c>
-      <c r="C143" s="40" t="n">
+      <c r="C143" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D143" s="34" t="n"/>
@@ -15805,7 +16482,7 @@
           <t>Parametric differentiation</t>
         </is>
       </c>
-      <c r="C144" s="40" t="n">
+      <c r="C144" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D144" s="34" t="n"/>
@@ -15877,7 +16554,7 @@
           <t>Implicit differentiation</t>
         </is>
       </c>
-      <c r="C145" s="40" t="n">
+      <c r="C145" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D145" s="34" t="n"/>
@@ -15949,7 +16626,7 @@
           <t>Constructing differential equations</t>
         </is>
       </c>
-      <c r="C146" s="40" t="n">
+      <c r="C146" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D146" s="34" t="n"/>
@@ -16483,7 +17160,7 @@
           <t>Integrating standard functions (eˣ, 1/x, sin, cos, sec² …)</t>
         </is>
       </c>
-      <c r="C155" s="40" t="n">
+      <c r="C155" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D155" s="34" t="n"/>
@@ -16544,7 +17221,7 @@
         </is>
       </c>
     </row>
-    <row r="156" outlineLevel="1" ht="20" customHeight="1">
+    <row r="156" outlineLevel="1" ht="32" customHeight="1">
       <c r="A156" s="31" t="inlineStr">
         <is>
           <t>P8.2</t>
@@ -16555,7 +17232,7 @@
           <t>Integrating f(ax + b)</t>
         </is>
       </c>
-      <c r="C156" s="40" t="n">
+      <c r="C156" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D156" s="34" t="n"/>
@@ -16575,18 +17252,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I156" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J156" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K156" s="39" t="n"/>
-      <c r="L156" s="39" t="n"/>
+      <c r="I156" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Integrating functions of ax + b (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J156" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 3 +3</t>
+        </is>
+      </c>
+      <c r="K156" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L156" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M156" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch11</t>
@@ -16608,7 +17293,7 @@
         </is>
       </c>
     </row>
-    <row r="157" outlineLevel="1" ht="20" customHeight="1">
+    <row r="157" outlineLevel="1" ht="32" customHeight="1">
       <c r="A157" s="31" t="inlineStr">
         <is>
           <t>P8.2</t>
@@ -16619,7 +17304,7 @@
           <t>Integration using trig identities (e.g. sin²x, tan²x)</t>
         </is>
       </c>
-      <c r="C157" s="40" t="n">
+      <c r="C157" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D157" s="34" t="n"/>
@@ -16639,18 +17324,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I157" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J157" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K157" s="39" t="n"/>
-      <c r="L157" s="39" t="n"/>
+      <c r="I157" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Integrating trigonometric functions (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J157" s="36" t="inlineStr">
+        <is>
+          <t>Q 3, 4, 5 +1</t>
+        </is>
+      </c>
+      <c r="K157" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L157" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M157" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch11</t>
@@ -16672,7 +17365,7 @@
         </is>
       </c>
     </row>
-    <row r="158" outlineLevel="1" ht="20" customHeight="1">
+    <row r="158" outlineLevel="1" ht="32" customHeight="1">
       <c r="A158" s="31" t="inlineStr">
         <is>
           <t>P8.5</t>
@@ -16683,7 +17376,7 @@
           <t>Reverse chain rule (f′(x)/f(x) and f′(x)[f(x)]ⁿ)</t>
         </is>
       </c>
-      <c r="C158" s="40" t="n">
+      <c r="C158" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D158" s="34" t="n"/>
@@ -16703,18 +17396,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I158" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J158" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K158" s="39" t="n"/>
-      <c r="L158" s="39" t="n"/>
+      <c r="I158" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Integration by substitution (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J158" s="36" t="inlineStr">
+        <is>
+          <t>Q 6, 7, 8</t>
+        </is>
+      </c>
+      <c r="K158" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L158" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M158" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch11</t>
@@ -16747,7 +17448,7 @@
           <t>Integration by substitution</t>
         </is>
       </c>
-      <c r="C159" s="40" t="n">
+      <c r="C159" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D159" s="34" t="n"/>
@@ -16819,7 +17520,7 @@
           <t>Integration by parts</t>
         </is>
       </c>
-      <c r="C160" s="40" t="n">
+      <c r="C160" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D160" s="34" t="n"/>
@@ -16891,7 +17592,7 @@
           <t>Integration using partial fractions</t>
         </is>
       </c>
-      <c r="C161" s="40" t="n">
+      <c r="C161" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D161" s="34" t="n"/>
@@ -16952,7 +17653,7 @@
         </is>
       </c>
     </row>
-    <row r="162" outlineLevel="1" ht="20" customHeight="1">
+    <row r="162" outlineLevel="1" ht="32" customHeight="1">
       <c r="A162" s="31" t="inlineStr">
         <is>
           <t>P8.3</t>
@@ -16960,10 +17661,10 @@
       </c>
       <c r="B162" s="32" t="inlineStr">
         <is>
-          <t>Areas between two curves (Year 2 functions)</t>
-        </is>
-      </c>
-      <c r="C162" s="40" t="n">
+          <t>Areas between a curve and a line, or two curves (Year 2 functions)</t>
+        </is>
+      </c>
+      <c r="C162" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D162" s="34" t="n"/>
@@ -16983,18 +17684,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I162" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J162" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K162" s="39" t="n"/>
-      <c r="L162" s="39" t="n"/>
+      <c r="I162" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Finding Areas using Integration 2 (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J162" s="36" t="inlineStr">
+        <is>
+          <t>pp 5, 8, 11</t>
+        </is>
+      </c>
+      <c r="K162" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L162" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M162" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch11</t>
@@ -17027,7 +17736,7 @@
           <t>Integration as the limit of a sum</t>
         </is>
       </c>
-      <c r="C163" s="40" t="n">
+      <c r="C163" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D163" s="34" t="n"/>
@@ -17099,7 +17808,7 @@
           <t>Area under a parametric curve</t>
         </is>
       </c>
-      <c r="C164" s="40" t="n">
+      <c r="C164" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D164" s="34" t="n"/>
@@ -17171,7 +17880,7 @@
           <t>Solving separable differential equations (incl. families of solution curves)</t>
         </is>
       </c>
-      <c r="C165" s="40" t="n">
+      <c r="C165" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D165" s="34" t="n"/>
@@ -17243,7 +17952,7 @@
           <t>Modelling with differential equations (interpreting solutions)</t>
         </is>
       </c>
-      <c r="C166" s="40" t="n">
+      <c r="C166" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D166" s="34" t="n"/>
@@ -17345,7 +18054,7 @@
           <t>Locating roots (change of sign) and when it fails</t>
         </is>
       </c>
-      <c r="C169" s="40" t="n">
+      <c r="C169" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D169" s="34" t="n"/>
@@ -17417,7 +18126,7 @@
           <t>Iteration xₙ₊₁ = g(xₙ), cobweb and staircase diagrams (incl. when it fails)</t>
         </is>
       </c>
-      <c r="C170" s="40" t="n">
+      <c r="C170" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D170" s="34" t="n"/>
@@ -17489,7 +18198,7 @@
           <t>The Newton-Raphson method</t>
         </is>
       </c>
-      <c r="C171" s="40" t="n">
+      <c r="C171" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D171" s="34" t="n"/>
@@ -17561,7 +18270,7 @@
           <t>The trapezium rule (over- and under-estimates)</t>
         </is>
       </c>
-      <c r="C172" s="40" t="n">
+      <c r="C172" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D172" s="34" t="n"/>
@@ -17633,7 +18342,7 @@
           <t>Numerical methods in context</t>
         </is>
       </c>
-      <c r="C173" s="40" t="n">
+      <c r="C173" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D173" s="34" t="n"/>
@@ -17724,7 +18433,7 @@
       <c r="N175" s="29" t="n"/>
       <c r="O175" s="29" t="n"/>
     </row>
-    <row r="176" outlineLevel="1" ht="20" customHeight="1">
+    <row r="176" outlineLevel="1" ht="32" customHeight="1">
       <c r="A176" s="31" t="inlineStr">
         <is>
           <t>P10.1</t>
@@ -17745,35 +18454,43 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G176" s="38" t="inlineStr">
+      <c r="G176" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H176" s="39" t="n"/>
-      <c r="I176" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J176" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K176" s="39" t="n"/>
-      <c r="L176" s="39" t="n"/>
+      <c r="H176" s="40" t="n"/>
+      <c r="I176" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Cartesian components of a vector</t>
+        </is>
+      </c>
+      <c r="J176" s="36" t="inlineStr">
+        <is>
+          <t>Q 1, 2, 7 +2</t>
+        </is>
+      </c>
+      <c r="K176" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L176" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M176" s="31" t="inlineStr">
         <is>
           <t>Pure 1 Ch11</t>
         </is>
       </c>
-      <c r="N176" s="38" t="inlineStr">
+      <c r="N176" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O176" s="41" t="n"/>
+      <c r="O176" s="39" t="n"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>P10</t>
@@ -18151,7 +18868,7 @@
           <t>3D coordinates and vectors in 3D (i, j, k)</t>
         </is>
       </c>
-      <c r="C182" s="40" t="n">
+      <c r="C182" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D182" s="34" t="n"/>
@@ -18223,7 +18940,7 @@
           <t>Solving geometric problems in 3D</t>
         </is>
       </c>
-      <c r="C183" s="40" t="n">
+      <c r="C183" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D183" s="34" t="n"/>
@@ -18284,7 +19001,7 @@
         </is>
       </c>
     </row>
-    <row r="184" outlineLevel="1" ht="20" customHeight="1">
+    <row r="184" outlineLevel="1" ht="32" customHeight="1">
       <c r="A184" s="31" t="inlineStr">
         <is>
           <t>P10.5</t>
@@ -18295,7 +19012,7 @@
           <t>3D vectors applied to mechanics</t>
         </is>
       </c>
-      <c r="C184" s="40" t="n">
+      <c r="C184" s="38" t="n">
         <v>2</v>
       </c>
       <c r="D184" s="34" t="n"/>
@@ -18315,29 +19032,37 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I184" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J184" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K184" s="39" t="n"/>
-      <c r="L184" s="39" t="n"/>
+      <c r="I184" s="35" t="inlineStr">
+        <is>
+          <t>Solomon: Cartesian components of a vector</t>
+        </is>
+      </c>
+      <c r="J184" s="36" t="inlineStr">
+        <is>
+          <t>Q 21</t>
+        </is>
+      </c>
+      <c r="K184" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L184" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M184" s="31" t="inlineStr">
         <is>
           <t>Pure 2 Ch12</t>
         </is>
       </c>
-      <c r="N184" s="38" t="inlineStr">
+      <c r="N184" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O184" s="41" t="n"/>
+      <c r="O184" s="39" t="n"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>P10</t>
@@ -18390,1081 +19115,1151 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N84" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N97" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N99" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N101" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N103" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N104" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N105" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N106" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N107" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N108" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N112" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N113" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N117" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N118" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N119" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N121" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N122" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N123" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N126" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N127" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N131" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N132" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N133" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N134" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N135" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N136" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N137" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N138" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N139" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N140" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N141" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N142" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N143" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N145" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N149" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N150" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N152" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N153" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N155" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N157" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N158" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N159" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N160" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N161" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N162" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N163" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N164" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N165" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N166" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N169" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N170" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N171" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N172" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N173" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N177" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N178" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N179" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N180" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N181" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N182" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N183" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N84" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N97" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N99" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N101" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N103" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N104" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N105" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N106" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N107" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N108" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N112" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N113" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N117" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N118" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N119" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N121" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N122" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N123" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N126" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N127" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N131" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N132" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N133" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N134" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N135" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N136" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N137" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N138" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N139" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N140" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N141" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N142" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N143" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N145" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N149" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N150" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N152" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N153" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N155" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N157" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N158" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N159" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N160" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N161" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N162" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N163" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N164" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N165" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N166" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N169" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N170" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N171" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N172" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N173" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N177" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N178" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N179" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N180" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N181" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N182" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N183" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId1156"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -19692,18 +20487,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I9" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J9" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K9" s="39" t="n"/>
-      <c r="L9" s="39" t="n"/>
+      <c r="I9" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Sampling methods 1</t>
+        </is>
+      </c>
+      <c r="J9" s="36" t="inlineStr">
+        <is>
+          <t>pp 1, 2, 3 +2</t>
+        </is>
+      </c>
+      <c r="K9" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L9" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M9" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch1</t>
@@ -19756,18 +20559,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I10" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J10" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K10" s="39" t="n"/>
-      <c r="L10" s="39" t="n"/>
+      <c r="I10" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Sampling methods 2</t>
+        </is>
+      </c>
+      <c r="J10" s="36" t="inlineStr">
+        <is>
+          <t>pp 1, 2, 3 +2</t>
+        </is>
+      </c>
+      <c r="K10" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L10" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M10" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch1</t>
@@ -19820,18 +20631,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I11" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J11" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K11" s="39" t="n"/>
-      <c r="L11" s="39" t="n"/>
+      <c r="I11" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Sampling methods 2</t>
+        </is>
+      </c>
+      <c r="J11" s="36" t="inlineStr">
+        <is>
+          <t>pp 2, 3, 4 +1</t>
+        </is>
+      </c>
+      <c r="K11" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L11" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M11" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch1</t>
@@ -19904,35 +20723,35 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G14" s="38" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H14" s="39" t="n"/>
-      <c r="I14" s="37" t="inlineStr">
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J14" s="38" t="inlineStr">
+      <c r="J14" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
+      <c r="K14" s="40" t="n"/>
+      <c r="L14" s="40" t="n"/>
       <c r="M14" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch1</t>
         </is>
       </c>
-      <c r="N14" s="38" t="inlineStr">
+      <c r="N14" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O14" s="41" t="n"/>
+      <c r="O14" s="39" t="n"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>S2</t>
@@ -20227,7 +21046,7 @@
         </is>
       </c>
     </row>
-    <row r="19" outlineLevel="1" ht="20" customHeight="1">
+    <row r="19" outlineLevel="1" ht="32" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>S2.1</t>
@@ -20258,18 +21077,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I19" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J19" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K19" s="39" t="n"/>
-      <c r="L19" s="39" t="n"/>
+      <c r="I19" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Representation and summary data</t>
+        </is>
+      </c>
+      <c r="J19" s="36" t="inlineStr">
+        <is>
+          <t>pp 13, 19, 24 +5</t>
+        </is>
+      </c>
+      <c r="K19" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L19" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M19" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch3</t>
@@ -20312,35 +21139,35 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G20" s="38" t="inlineStr">
+      <c r="G20" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H20" s="39" t="n"/>
-      <c r="I20" s="37" t="inlineStr">
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J20" s="38" t="inlineStr">
+      <c r="J20" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K20" s="39" t="n"/>
-      <c r="L20" s="39" t="n"/>
+      <c r="K20" s="40" t="n"/>
+      <c r="L20" s="40" t="n"/>
       <c r="M20" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch3</t>
         </is>
       </c>
-      <c r="N20" s="38" t="inlineStr">
+      <c r="N20" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O20" s="41" t="n"/>
+      <c r="O20" s="39" t="n"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>S2</t>
@@ -20763,12 +21590,12 @@
           <t>Applied 2 Ch1</t>
         </is>
       </c>
-      <c r="N26" s="38" t="inlineStr">
+      <c r="N26" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O26" s="41" t="n"/>
+      <c r="O26" s="39" t="n"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>S2</t>
@@ -20796,12 +21623,12 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G27" s="38" t="inlineStr">
+      <c r="G27" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H27" s="39" t="n"/>
+      <c r="H27" s="40" t="n"/>
       <c r="I27" s="35" t="inlineStr">
         <is>
           <t>Large data sets</t>
@@ -21480,18 +22307,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I38" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J38" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K38" s="39" t="n"/>
-      <c r="L38" s="39" t="n"/>
+      <c r="I38" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Probability (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J38" s="36" t="inlineStr">
+        <is>
+          <t>pp 1, 4, 8 +2</t>
+        </is>
+      </c>
+      <c r="K38" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L38" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M38" s="31" t="inlineStr">
         <is>
           <t>Applied 2 Ch2</t>
@@ -22068,12 +22903,12 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G48" s="38" t="inlineStr">
+      <c r="G48" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H48" s="39" t="n"/>
+      <c r="H48" s="40" t="n"/>
       <c r="I48" s="35" t="inlineStr">
         <is>
           <t>Binomial Distribution (Yr 2)</t>
@@ -22759,304 +23594,309 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId306"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -23448,12 +24288,12 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G13" s="38" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H13" s="39" t="n"/>
+      <c r="H13" s="40" t="n"/>
       <c r="I13" s="35" t="inlineStr">
         <is>
           <t>suvat</t>
@@ -23516,35 +24356,35 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G14" s="38" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H14" s="39" t="n"/>
-      <c r="I14" s="37" t="inlineStr">
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J14" s="38" t="inlineStr">
+      <c r="J14" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
+      <c r="K14" s="40" t="n"/>
+      <c r="L14" s="40" t="n"/>
       <c r="M14" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch9</t>
         </is>
       </c>
-      <c r="N14" s="38" t="inlineStr">
+      <c r="N14" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O14" s="41" t="n"/>
+      <c r="O14" s="39" t="n"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>M7</t>
@@ -23942,18 +24782,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I20" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J20" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K20" s="39" t="n"/>
-      <c r="L20" s="39" t="n"/>
+      <c r="I20" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Problems with calculus</t>
+        </is>
+      </c>
+      <c r="J20" s="36" t="inlineStr">
+        <is>
+          <t>pp 1, 2</t>
+        </is>
+      </c>
+      <c r="K20" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L20" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M20" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch11</t>
@@ -24068,24 +24916,32 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G22" s="38" t="inlineStr">
+      <c r="G22" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H22" s="39" t="n"/>
-      <c r="I22" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J22" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K22" s="39" t="n"/>
-      <c r="L22" s="39" t="n"/>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="35" t="inlineStr">
+        <is>
+          <t>Set B: Motion Graphs</t>
+        </is>
+      </c>
+      <c r="J22" s="36" t="inlineStr">
+        <is>
+          <t>p 1</t>
+        </is>
+      </c>
+      <c r="K22" s="37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L22" s="36" t="inlineStr">
+        <is>
+          <t>Answers</t>
+        </is>
+      </c>
       <c r="M22" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch11</t>
@@ -24272,24 +25128,32 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G25" s="38" t="inlineStr">
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H25" s="39" t="n"/>
-      <c r="I25" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J25" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K25" s="39" t="n"/>
-      <c r="L25" s="39" t="n"/>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Projectiles 2 (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J25" s="36" t="inlineStr">
+        <is>
+          <t>p 9</t>
+        </is>
+      </c>
+      <c r="K25" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L25" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M25" s="31" t="inlineStr">
         <is>
           <t>Applied 2 Ch6</t>
@@ -24516,29 +25380,29 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I30" s="37" t="inlineStr">
+      <c r="I30" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J30" s="38" t="inlineStr">
+      <c r="J30" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K30" s="39" t="n"/>
-      <c r="L30" s="39" t="n"/>
+      <c r="K30" s="40" t="n"/>
+      <c r="L30" s="40" t="n"/>
       <c r="M30" s="31" t="inlineStr">
         <is>
           <t>Applied 1 Ch10</t>
         </is>
       </c>
-      <c r="N30" s="38" t="inlineStr">
+      <c r="N30" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O30" s="41" t="n"/>
+      <c r="O30" s="39" t="n"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>M8</t>
@@ -25532,35 +26396,35 @@
           <t>▶ Watch</t>
         </is>
       </c>
-      <c r="G46" s="38" t="inlineStr">
+      <c r="G46" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="H46" s="39" t="n"/>
-      <c r="I46" s="37" t="inlineStr">
+      <c r="H46" s="40" t="n"/>
+      <c r="I46" s="41" t="inlineStr">
         <is>
           <t>none for this topic</t>
         </is>
       </c>
-      <c r="J46" s="38" t="inlineStr">
+      <c r="J46" s="37" t="inlineStr">
         <is>
           <t>none on this topic</t>
         </is>
       </c>
-      <c r="K46" s="39" t="n"/>
-      <c r="L46" s="39" t="n"/>
+      <c r="K46" s="40" t="n"/>
+      <c r="L46" s="40" t="n"/>
       <c r="M46" s="31" t="inlineStr">
         <is>
           <t>Applied 2 Ch4</t>
         </is>
       </c>
-      <c r="N46" s="38" t="inlineStr">
+      <c r="N46" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O46" s="41" t="n"/>
+      <c r="O46" s="39" t="n"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>M9</t>
@@ -25639,7 +26503,7 @@
         </is>
       </c>
     </row>
-    <row r="48" outlineLevel="1" ht="20" customHeight="1">
+    <row r="48" outlineLevel="1" ht="32" customHeight="1">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>M9.1</t>
@@ -25670,18 +26534,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I48" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J48" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K48" s="39" t="n"/>
-      <c r="L48" s="39" t="n"/>
+      <c r="I48" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Moments - Moments about a point 1 (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J48" s="36" t="inlineStr">
+        <is>
+          <t>pp 5, 9</t>
+        </is>
+      </c>
+      <c r="K48" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L48" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M48" s="31" t="inlineStr">
         <is>
           <t>Applied 2 Ch4</t>
@@ -25703,7 +26575,7 @@
         </is>
       </c>
     </row>
-    <row r="49" outlineLevel="1" ht="20" customHeight="1">
+    <row r="49" outlineLevel="1" ht="32" customHeight="1">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>M9.1</t>
@@ -25734,18 +26606,26 @@
           <t>Answers</t>
         </is>
       </c>
-      <c r="I49" s="37" t="inlineStr">
-        <is>
-          <t>none for this topic</t>
-        </is>
-      </c>
-      <c r="J49" s="38" t="inlineStr">
-        <is>
-          <t>none on this topic</t>
-        </is>
-      </c>
-      <c r="K49" s="39" t="n"/>
-      <c r="L49" s="39" t="n"/>
+      <c r="I49" s="35" t="inlineStr">
+        <is>
+          <t>Set A: Moments - Moments about a point 1 (Yr 2)</t>
+        </is>
+      </c>
+      <c r="J49" s="36" t="inlineStr">
+        <is>
+          <t>pp 3, 6, 7 +1</t>
+        </is>
+      </c>
+      <c r="K49" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
+      <c r="L49" s="37" t="inlineStr">
+        <is>
+          <t>in the PDF</t>
+        </is>
+      </c>
       <c r="M49" s="31" t="inlineStr">
         <is>
           <t>Applied 2 Ch4</t>
@@ -25940,188 +26820,194 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId254"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -26251,8 +27137,8 @@
         </is>
       </c>
       <c r="F7" s="65" t="n"/>
-      <c r="G7" s="39" t="n"/>
-      <c r="H7" s="39" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="40" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="64" t="inlineStr">
@@ -26281,8 +27167,8 @@
         </is>
       </c>
       <c r="F8" s="65" t="n"/>
-      <c r="G8" s="39" t="n"/>
-      <c r="H8" s="39" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="40" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="64" t="inlineStr">
@@ -26300,15 +27186,15 @@
           <t>Textbook review exercise 1 - pg.85-88</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E9" s="41" t="n"/>
+      <c r="E9" s="39" t="n"/>
       <c r="F9" s="65" t="n"/>
-      <c r="G9" s="39" t="n"/>
-      <c r="H9" s="39" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="40" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="64" t="inlineStr">
@@ -26337,8 +27223,8 @@
         </is>
       </c>
       <c r="F10" s="65" t="n"/>
-      <c r="G10" s="39" t="n"/>
-      <c r="H10" s="39" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="40" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="64" t="inlineStr">
@@ -26367,8 +27253,8 @@
         </is>
       </c>
       <c r="F11" s="65" t="n"/>
-      <c r="G11" s="39" t="n"/>
-      <c r="H11" s="39" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="40" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="64" t="inlineStr">
@@ -26397,8 +27283,8 @@
         </is>
       </c>
       <c r="F12" s="65" t="n"/>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="40" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="64" t="inlineStr">
@@ -26427,8 +27313,8 @@
         </is>
       </c>
       <c r="F13" s="65" t="n"/>
-      <c r="G13" s="39" t="n"/>
-      <c r="H13" s="39" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="40" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="64" t="inlineStr">
@@ -26457,8 +27343,8 @@
         </is>
       </c>
       <c r="F14" s="65" t="n"/>
-      <c r="G14" s="39" t="n"/>
-      <c r="H14" s="39" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="40" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="64" t="inlineStr">
@@ -26487,8 +27373,8 @@
         </is>
       </c>
       <c r="F15" s="65" t="n"/>
-      <c r="G15" s="39" t="n"/>
-      <c r="H15" s="39" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="64" t="inlineStr">
@@ -26517,8 +27403,8 @@
         </is>
       </c>
       <c r="F16" s="65" t="n"/>
-      <c r="G16" s="39" t="n"/>
-      <c r="H16" s="39" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="40" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="64" t="inlineStr">
@@ -26536,15 +27422,15 @@
           <t>Textbook review exercise 2 - pg.226 - 229</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E17" s="41" t="n"/>
+      <c r="E17" s="39" t="n"/>
       <c r="F17" s="65" t="n"/>
-      <c r="G17" s="39" t="n"/>
-      <c r="H17" s="39" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="40" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="64" t="inlineStr">
@@ -26573,8 +27459,8 @@
         </is>
       </c>
       <c r="F18" s="65" t="n"/>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="39" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="40" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="64" t="inlineStr">
@@ -26603,8 +27489,8 @@
         </is>
       </c>
       <c r="F19" s="65" t="n"/>
-      <c r="G19" s="39" t="n"/>
-      <c r="H19" s="39" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="40" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="64" t="inlineStr">
@@ -26633,8 +27519,8 @@
         </is>
       </c>
       <c r="F20" s="65" t="n"/>
-      <c r="G20" s="39" t="n"/>
-      <c r="H20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="64" t="inlineStr">
@@ -26663,8 +27549,8 @@
         </is>
       </c>
       <c r="F21" s="65" t="n"/>
-      <c r="G21" s="39" t="n"/>
-      <c r="H21" s="39" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="40" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="64" t="inlineStr">
@@ -26693,8 +27579,8 @@
         </is>
       </c>
       <c r="F22" s="65" t="n"/>
-      <c r="G22" s="39" t="n"/>
-      <c r="H22" s="39" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="40" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="64" t="inlineStr">
@@ -26723,8 +27609,8 @@
         </is>
       </c>
       <c r="F23" s="65" t="n"/>
-      <c r="G23" s="39" t="n"/>
-      <c r="H23" s="39" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="40" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="64" t="inlineStr">
@@ -26742,15 +27628,15 @@
           <t>Textbook review exercise 3 - pg.338-341</t>
         </is>
       </c>
-      <c r="D24" s="38" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E24" s="41" t="n"/>
+      <c r="E24" s="39" t="n"/>
       <c r="F24" s="65" t="n"/>
-      <c r="G24" s="39" t="n"/>
-      <c r="H24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="64" t="inlineStr">
@@ -26779,8 +27665,8 @@
         </is>
       </c>
       <c r="F25" s="65" t="n"/>
-      <c r="G25" s="39" t="n"/>
-      <c r="H25" s="39" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="40" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="64" t="inlineStr">
@@ -26809,8 +27695,8 @@
         </is>
       </c>
       <c r="F26" s="65" t="n"/>
-      <c r="G26" s="39" t="n"/>
-      <c r="H26" s="39" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="40" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="64" t="inlineStr">
@@ -26839,8 +27725,8 @@
         </is>
       </c>
       <c r="F27" s="65" t="n"/>
-      <c r="G27" s="39" t="n"/>
-      <c r="H27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="40" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="64" t="inlineStr">
@@ -26869,8 +27755,8 @@
         </is>
       </c>
       <c r="F28" s="65" t="n"/>
-      <c r="G28" s="39" t="n"/>
-      <c r="H28" s="39" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="40" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="64" t="inlineStr">
@@ -26899,8 +27785,8 @@
         </is>
       </c>
       <c r="F29" s="65" t="n"/>
-      <c r="G29" s="39" t="n"/>
-      <c r="H29" s="39" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="40" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="64" t="inlineStr">
@@ -26923,14 +27809,14 @@
           <t>Questions</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr">
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
       <c r="F30" s="65" t="n"/>
-      <c r="G30" s="39" t="n"/>
-      <c r="H30" s="39" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="40" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="64" t="inlineStr">
@@ -26948,15 +27834,15 @@
           <t>Textbook review exercise 1 - pg.107-112</t>
         </is>
       </c>
-      <c r="D31" s="38" t="inlineStr">
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E31" s="41" t="n"/>
+      <c r="E31" s="39" t="n"/>
       <c r="F31" s="65" t="n"/>
-      <c r="G31" s="39" t="n"/>
-      <c r="H31" s="39" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="40" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="64" t="inlineStr">
@@ -26985,8 +27871,8 @@
         </is>
       </c>
       <c r="F32" s="65" t="n"/>
-      <c r="G32" s="39" t="n"/>
-      <c r="H32" s="39" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="40" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="64" t="inlineStr">
@@ -27015,8 +27901,8 @@
         </is>
       </c>
       <c r="F33" s="65" t="n"/>
-      <c r="G33" s="39" t="n"/>
-      <c r="H33" s="39" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="40" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="64" t="inlineStr">
@@ -27045,8 +27931,8 @@
         </is>
       </c>
       <c r="F34" s="65" t="n"/>
-      <c r="G34" s="39" t="n"/>
-      <c r="H34" s="39" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="40" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="64" t="inlineStr">
@@ -27075,8 +27961,8 @@
         </is>
       </c>
       <c r="F35" s="65" t="n"/>
-      <c r="G35" s="39" t="n"/>
-      <c r="H35" s="39" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="40" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="64" t="inlineStr">
@@ -27094,15 +27980,15 @@
           <t>Textbook review exercise 2 - pg.225-230</t>
         </is>
       </c>
-      <c r="D36" s="38" t="inlineStr">
+      <c r="D36" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E36" s="41" t="n"/>
+      <c r="E36" s="39" t="n"/>
       <c r="F36" s="65" t="n"/>
-      <c r="G36" s="39" t="n"/>
-      <c r="H36" s="39" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="40" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="64" t="inlineStr">
@@ -27131,8 +28017,8 @@
         </is>
       </c>
       <c r="F37" s="65" t="n"/>
-      <c r="G37" s="39" t="n"/>
-      <c r="H37" s="39" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="40" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="64" t="inlineStr">
@@ -27161,8 +28047,8 @@
         </is>
       </c>
       <c r="F38" s="65" t="n"/>
-      <c r="G38" s="39" t="n"/>
-      <c r="H38" s="39" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="40" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="64" t="inlineStr">
@@ -27191,8 +28077,8 @@
         </is>
       </c>
       <c r="F39" s="65" t="n"/>
-      <c r="G39" s="39" t="n"/>
-      <c r="H39" s="39" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="40" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="64" t="inlineStr">
@@ -27221,8 +28107,8 @@
         </is>
       </c>
       <c r="F40" s="65" t="n"/>
-      <c r="G40" s="39" t="n"/>
-      <c r="H40" s="39" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="40" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="64" t="inlineStr">
@@ -27251,7 +28137,7 @@
         </is>
       </c>
       <c r="F41" s="65" t="n"/>
-      <c r="G41" s="39" t="n"/>
+      <c r="G41" s="40" t="n"/>
       <c r="H41" s="67" t="inlineStr">
         <is>
           <t>p5 Q13(d), p9 Q8(b): volumes of revolution</t>
@@ -27285,8 +28171,8 @@
         </is>
       </c>
       <c r="F42" s="65" t="n"/>
-      <c r="G42" s="39" t="n"/>
-      <c r="H42" s="39" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="40" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="64" t="inlineStr">
@@ -27315,7 +28201,7 @@
         </is>
       </c>
       <c r="F43" s="65" t="n"/>
-      <c r="G43" s="39" t="n"/>
+      <c r="G43" s="40" t="n"/>
       <c r="H43" s="67" t="inlineStr">
         <is>
           <t>p3 Q12, p6 Q7(b): volumes of revolution</t>
@@ -27349,8 +28235,8 @@
         </is>
       </c>
       <c r="F44" s="65" t="n"/>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="39" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="40" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="64" t="inlineStr">
@@ -27368,15 +28254,15 @@
           <t>Textbook review exercise 3 - pg.352-357</t>
         </is>
       </c>
-      <c r="D45" s="38" t="inlineStr">
+      <c r="D45" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E45" s="41" t="n"/>
+      <c r="E45" s="39" t="n"/>
       <c r="F45" s="65" t="n"/>
-      <c r="G45" s="39" t="n"/>
-      <c r="H45" s="39" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="40" t="n"/>
     </row>
     <row r="46" ht="10" customHeight="1"/>
     <row r="47" ht="26" customHeight="1">
@@ -27424,7 +28310,7 @@
         </is>
       </c>
       <c r="F48" s="65" t="n"/>
-      <c r="G48" s="39" t="n"/>
+      <c r="G48" s="40" t="n"/>
       <c r="H48" s="67" t="inlineStr">
         <is>
           <t>p11 Q2 and p13 Q1, skewness parts only</t>
@@ -27458,7 +28344,7 @@
         </is>
       </c>
       <c r="F49" s="65" t="n"/>
-      <c r="G49" s="39" t="n"/>
+      <c r="G49" s="40" t="n"/>
       <c r="H49" s="67" t="inlineStr">
         <is>
           <t>p12 Q2(d), p14 Q1(e): skewness</t>
@@ -27492,8 +28378,8 @@
         </is>
       </c>
       <c r="F50" s="65" t="n"/>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="39" t="n"/>
+      <c r="G50" s="40" t="n"/>
+      <c r="H50" s="40" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="64" t="inlineStr">
@@ -27522,8 +28408,8 @@
         </is>
       </c>
       <c r="F51" s="65" t="n"/>
-      <c r="G51" s="39" t="n"/>
-      <c r="H51" s="39" t="n"/>
+      <c r="G51" s="40" t="n"/>
+      <c r="H51" s="40" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="64" t="inlineStr">
@@ -27552,7 +28438,7 @@
         </is>
       </c>
       <c r="F52" s="65" t="n"/>
-      <c r="G52" s="39" t="n"/>
+      <c r="G52" s="40" t="n"/>
       <c r="H52" s="67" t="inlineStr">
         <is>
           <t>p7 Q1 and p10 Q6: Poisson distribution</t>
@@ -27575,15 +28461,15 @@
           <t>Textbook review exercise 1 - pg. 113-117</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
+      <c r="D53" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E53" s="41" t="n"/>
+      <c r="E53" s="39" t="n"/>
       <c r="F53" s="65" t="n"/>
-      <c r="G53" s="39" t="n"/>
-      <c r="H53" s="39" t="n"/>
+      <c r="G53" s="40" t="n"/>
+      <c r="H53" s="40" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="64" t="inlineStr">
@@ -27612,8 +28498,8 @@
         </is>
       </c>
       <c r="F54" s="65" t="n"/>
-      <c r="G54" s="39" t="n"/>
-      <c r="H54" s="39" t="n"/>
+      <c r="G54" s="40" t="n"/>
+      <c r="H54" s="40" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="64" t="inlineStr">
@@ -27642,8 +28528,8 @@
         </is>
       </c>
       <c r="F55" s="65" t="n"/>
-      <c r="G55" s="39" t="n"/>
-      <c r="H55" s="39" t="n"/>
+      <c r="G55" s="40" t="n"/>
+      <c r="H55" s="40" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="64" t="inlineStr">
@@ -27672,7 +28558,7 @@
         </is>
       </c>
       <c r="F56" s="65" t="n"/>
-      <c r="G56" s="39" t="n"/>
+      <c r="G56" s="40" t="n"/>
       <c r="H56" s="67" t="inlineStr">
         <is>
           <t>p8 Q1(c), p10 Q1(b), p12 Q4(b), p15 Q6, p16 Q1(b): Poisson</t>
@@ -27695,15 +28581,15 @@
           <t>Textbook review exercise 1 - pg.65-69</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr">
+      <c r="D57" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E57" s="41" t="n"/>
+      <c r="E57" s="39" t="n"/>
       <c r="F57" s="65" t="n"/>
-      <c r="G57" s="39" t="n"/>
-      <c r="H57" s="39" t="n"/>
+      <c r="G57" s="40" t="n"/>
+      <c r="H57" s="40" t="n"/>
     </row>
     <row r="58" ht="10" customHeight="1"/>
     <row r="59" ht="26" customHeight="1">
@@ -27751,8 +28637,8 @@
         </is>
       </c>
       <c r="F60" s="65" t="n"/>
-      <c r="G60" s="39" t="n"/>
-      <c r="H60" s="39" t="n"/>
+      <c r="G60" s="40" t="n"/>
+      <c r="H60" s="40" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="64" t="inlineStr">
@@ -27781,8 +28667,8 @@
         </is>
       </c>
       <c r="F61" s="65" t="n"/>
-      <c r="G61" s="39" t="n"/>
-      <c r="H61" s="39" t="n"/>
+      <c r="G61" s="40" t="n"/>
+      <c r="H61" s="40" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="64" t="inlineStr">
@@ -27811,7 +28697,7 @@
         </is>
       </c>
       <c r="F62" s="65" t="n"/>
-      <c r="G62" s="39" t="n"/>
+      <c r="G62" s="40" t="n"/>
       <c r="H62" s="67" t="inlineStr">
         <is>
           <t>p7 Q3(b): momentum</t>
@@ -27845,8 +28731,8 @@
         </is>
       </c>
       <c r="F63" s="65" t="n"/>
-      <c r="G63" s="39" t="n"/>
-      <c r="H63" s="39" t="n"/>
+      <c r="G63" s="40" t="n"/>
+      <c r="H63" s="40" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="64" t="inlineStr">
@@ -27864,15 +28750,15 @@
           <t>Textbook review exercise 2 - pg. 197-200</t>
         </is>
       </c>
-      <c r="D64" s="38" t="inlineStr">
+      <c r="D64" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E64" s="41" t="n"/>
+      <c r="E64" s="39" t="n"/>
       <c r="F64" s="65" t="n"/>
-      <c r="G64" s="39" t="n"/>
-      <c r="H64" s="39" t="n"/>
+      <c r="G64" s="40" t="n"/>
+      <c r="H64" s="40" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="64" t="inlineStr">
@@ -27901,8 +28787,8 @@
         </is>
       </c>
       <c r="F65" s="65" t="n"/>
-      <c r="G65" s="39" t="n"/>
-      <c r="H65" s="39" t="n"/>
+      <c r="G65" s="40" t="n"/>
+      <c r="H65" s="40" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="64" t="inlineStr">
@@ -27931,8 +28817,8 @@
         </is>
       </c>
       <c r="F66" s="65" t="n"/>
-      <c r="G66" s="39" t="n"/>
-      <c r="H66" s="39" t="n"/>
+      <c r="G66" s="40" t="n"/>
+      <c r="H66" s="40" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="64" t="inlineStr">
@@ -27961,8 +28847,8 @@
         </is>
       </c>
       <c r="F67" s="65" t="n"/>
-      <c r="G67" s="39" t="n"/>
-      <c r="H67" s="39" t="n"/>
+      <c r="G67" s="40" t="n"/>
+      <c r="H67" s="40" t="n"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="64" t="inlineStr">
@@ -27991,8 +28877,8 @@
         </is>
       </c>
       <c r="F68" s="65" t="n"/>
-      <c r="G68" s="39" t="n"/>
-      <c r="H68" s="39" t="n"/>
+      <c r="G68" s="40" t="n"/>
+      <c r="H68" s="40" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="64" t="inlineStr">
@@ -28021,8 +28907,8 @@
         </is>
       </c>
       <c r="F69" s="65" t="n"/>
-      <c r="G69" s="39" t="n"/>
-      <c r="H69" s="39" t="n"/>
+      <c r="G69" s="40" t="n"/>
+      <c r="H69" s="40" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="64" t="inlineStr">
@@ -28051,8 +28937,8 @@
         </is>
       </c>
       <c r="F70" s="65" t="n"/>
-      <c r="G70" s="39" t="n"/>
-      <c r="H70" s="39" t="n"/>
+      <c r="G70" s="40" t="n"/>
+      <c r="H70" s="40" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="64" t="inlineStr">
@@ -28070,15 +28956,15 @@
           <t>Textbook review exercise 2 - pg.182-186</t>
         </is>
       </c>
-      <c r="D71" s="38" t="inlineStr">
+      <c r="D71" s="37" t="inlineStr">
         <is>
           <t>in the book</t>
         </is>
       </c>
-      <c r="E71" s="41" t="n"/>
+      <c r="E71" s="39" t="n"/>
       <c r="F71" s="65" t="n"/>
-      <c r="G71" s="39" t="n"/>
-      <c r="H71" s="39" t="n"/>
+      <c r="G71" s="40" t="n"/>
+      <c r="H71" s="40" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F5:F71">

--- a/Edexcel_A_Level_Maths_RAG.xlsx
+++ b/Edexcel_A_Level_Maths_RAG.xlsx
@@ -29282,7 +29282,7 @@
         </is>
       </c>
       <c r="B12" s="92">
-        <f>COUNTIFS('Pure'!$D$7:$D$184,"",'Pure'!$C$7:$C$184,"&gt;0")+COUNTIFS('Statistics'!$D$7:$D$58,"",'Statistics'!$C$7:$C$58,"&gt;0")+COUNTIFS('Mechanics'!$D$7:$D$50,"",'Mechanics'!$C$7:$C$50,"&gt;0")</f>
+        <f>COUNTIFS('Pure'!$C$7:$C$184,"&gt;0")+COUNTIFS('Statistics'!$C$7:$C$58,"&gt;0")+COUNTIFS('Mechanics'!$C$7:$C$50,"&gt;0")-B9-B10-B11</f>
         <v/>
       </c>
     </row>
